--- a/cases/03_模板示例/项目配置.xlsx
+++ b/cases/03_模板示例/项目配置.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>销售数据分析报告|2024年度经营数据全景</t>
+          <t>5G基站网络指标分析报告|2024年度网络运营数据全景</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>各地区销售业绩|按地区汇总销售额对比</t>
+          <t>各地区基站规模|按地区汇总基站数量对比</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>各地区销售额对比</t>
+          <t>各地区基站数量对比</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -617,7 +617,7 @@
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>销售额最高地区为 {max_cat}，达 {max_val:.1f} 万元；平均 {avg:.1f} 万元</t>
+          <t>基站数最多地区为 {max_cat}，达 {max_val} 个；平均 {avg:.0f} 个</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>类别与行业分布</t>
+          <t>频段与覆盖类型分布</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>类别销售统计</t>
+          <t>按频段汇总</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -657,17 +657,17 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>产品类别</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>产品类别销售额占比</t>
+          <t>各频段基站数占比</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>客户销售统计</t>
+          <t>站点用户统计</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>客户ID</t>
+          <t>站点ID</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>总用户数</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>客户销售额分布</t>
+          <t>站点用户数分布</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>月度业绩趋势|销售额、成本、利润走势</t>
+          <t>月度网络指标趋势|PRB利用率与下行速率走势</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>月度业绩</t>
+          <t>月度指标</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>销售额,成本,利润</t>
+          <t>下行PRB利用率,下行速率(Mbps)</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>月度业绩趋势</t>
+          <t>月度PRB与速率趋势</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>月度业绩</t>
+          <t>月度指标</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -801,12 +801,12 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>利润</t>
+          <t>流量(TB)</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>月度利润面积图</t>
+          <t>月度流量面积图</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>多维数据分析</t>
+          <t>多维网络数据分析</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>地区销售额条形图</t>
+          <t>地区基站数条形图</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>月度业绩</t>
+          <t>月度指标</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -898,17 +898,17 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>下行PRB利用率</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>利润</t>
+          <t>下行速率(Mbps)</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>销售额-利润散点图</t>
+          <t>PRB-速率散点图</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>月度业绩</t>
+          <t>月度指标</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -944,12 +944,12 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>销售额,订单数</t>
+          <t>连接用户数,流量(TB)</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>销售额与订单数组合图</t>
+          <t>用户数与流量组合图</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>按产品汇总</t>
+          <t>按频段汇总</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>产品名</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元),订单数</t>
+          <t>基站数,连接用户数</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>产品销售对比</t>
+          <t>各频段基站与用户对比</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>城市销售热力地图</t>
+          <t>城市基站热力地图</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>城市销售热力分布</t>
+          <t>城市基站热力分布</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>城市销售散点地图|按经纬度展示销售分布</t>
+          <t>城市基站散点地图|按经纬度展示基站分布</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>城市销售分布散点地图</t>
+          <t>城市基站分布散点地图</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>地区季度销售层级分析</t>
+          <t>地区季度基站层级分析</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>地区×季度销售层级图</t>
+          <t>地区×季度基站层级图</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -1164,7 +1164,7 @@
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>最高为 {max_cat}，销售额 {max_val:.1f} 万元</t>
+          <t>最高为 {max_cat}，基站数 {max_val}</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1304,12 +1304,12 @@
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站ID</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -1321,20 +1321,16 @@
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>/10000</t>
-        </is>
-      </c>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>各地区销售额汇总</t>
+          <t>各地区基站数量统计</t>
         </is>
       </c>
     </row>
@@ -1349,48 +1345,44 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>产品名</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>销售额,数量,销售额</t>
+          <t>基站ID,连接用户数,连接用户数</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>sum,count,avg</t>
+          <t>count,sum,avg</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>按产品汇总</t>
+          <t>按频段汇总</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元),订单数,平均单价</t>
+          <t>基站数,总用户数,平均用户数</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>/10000,,</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>产品销售多维统计</t>
+          <t>频段多维统计</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1397,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1415,38 +1407,34 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>产品类别</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站ID</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>地区产品交叉</t>
+          <t>地区频段交叉</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>/10000</t>
-        </is>
-      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>地区×产品交叉表</t>
+          <t>地区×频段交叉表</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1449,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1472,7 +1460,7 @@
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1482,14 +1470,14 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>地区占比</t>
+          <t>地区用户占比</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>销售额占比</t>
+          <t>用户占比</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
@@ -1498,7 +1486,7 @@
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>各地区销售额占比</t>
+          <t>各地区用户数占比</t>
         </is>
       </c>
     </row>
@@ -1513,18 +1501,18 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>产品类别</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1534,14 +1522,14 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>类别订单占比</t>
+          <t>频段基站占比</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>订单占比</t>
+          <t>基站占比</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
@@ -1550,7 +1538,7 @@
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>各类别订单计数占比</t>
+          <t>各频段基站计数占比</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1553,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1576,7 +1564,7 @@
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>客户ID</t>
+          <t>站点ID</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1586,14 +1574,14 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>客户去重计数</t>
+          <t>站点去重计数</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>客户数</t>
+          <t>站点数</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
@@ -1602,7 +1590,7 @@
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>各地区去重客户数</t>
+          <t>各地区去重站点数</t>
         </is>
       </c>
     </row>
@@ -1617,18 +1605,18 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>下行速率(Mbps)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>订单ID</t>
+          <t>基站ID</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1638,19 +1626,19 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>销售额分箱统计</t>
+          <t>速率分箱统计</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>订单数</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>销售额=0,50000,200000,5</t>
+          <t>下行速率(Mbps)=200,500,1000,5</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr"/>
@@ -1658,7 +1646,7 @@
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>销售额自动分箱</t>
+          <t>下行速率自动分箱</t>
         </is>
       </c>
     </row>
@@ -1673,40 +1661,40 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>上行PRB利用率</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站ID</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>数量分箱统计</t>
+          <t>PRB分箱统计</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>数量=10,30,50</t>
+          <t>上行PRB利用率=30,50,70,90</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr"/>
@@ -1714,7 +1702,7 @@
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>数量自定义断点分箱</t>
+          <t>上行PRB自定义分箱</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1717,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1740,12 +1728,12 @@
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>销售额,数量</t>
+          <t>连接用户数,下行速率(Mbps)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>sum,sum</t>
+          <t>sum,avg</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1757,20 +1745,20 @@
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元),数量(千件)</t>
+          <t>总用户数(千人),平均速率</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>/10000,/1000</t>
+          <t>/1000,</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>季度业绩汇总</t>
+          <t>季度指标汇总</t>
         </is>
       </c>
     </row>
@@ -1780,23 +1768,23 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>示例数据.xlsx@销售明细 JOIN 示例数据.xlsx@客户信息 ON 客户ID=客户ID</t>
+          <t>示例数据.xlsx@基站明细 JOIN 示例数据.xlsx@站点信息 ON 站点ID=站点ID</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>客户ID</t>
+          <t>站点ID</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1806,27 +1794,23 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>客户销售统计</t>
+          <t>站点用户统计</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>总用户数</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>/10000</t>
-        </is>
-      </c>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>INNER JOIN 客户信息按客户统计</t>
+          <t>INNER JOIN 站点信息按站点统计</t>
         </is>
       </c>
     </row>
@@ -1836,53 +1820,49 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>示例数据.xlsx@销售明细 LEFT JOIN 示例数据.xlsx@产品目录 ON 产品编码=产品编码</t>
+          <t>示例数据.xlsx@基站明细 LEFT JOIN 示例数据.xlsx@频段目录 ON 频段=频段</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>产品类别</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站ID</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>类别销售统计</t>
+          <t>频段带统计</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>/10000</t>
-        </is>
-      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>LEFT JOIN 产品目录按类别</t>
+          <t>LEFT JOIN 频段目录</t>
         </is>
       </c>
     </row>
@@ -1897,52 +1877,48 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>下行速率(Mbps)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>avg</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>大单销售员统计</t>
+          <t>高速率频段统计</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>平均速率</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>/10000</t>
-        </is>
-      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>销售额 &gt; 30000</t>
+          <t>下行速率(Mbps) &gt; 500</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>过滤大额订单</t>
+          <t>过滤高速率基站</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1933,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1968,36 +1944,32 @@
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站ID</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>重点订单统计</t>
+          <t>重点基站统计</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>/10000</t>
-        </is>
-      </c>
+      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>(地区 = '华北' AND 销售额 &gt; 20000) OR 产品名 包含 '手机'</t>
+          <t>(地区 = '华北' AND 连接用户数 &gt; 200) OR 覆盖类型 包含 '室内'</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2017,43 +1989,39 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>产品类别</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>下行速率(Mbps)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>sum,avg,max</t>
+          <t>avg,max,min</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>类别多维统计</t>
+          <t>速率多维统计</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>总额,均值,峰值</t>
+          <t>均值,峰值,谷值</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>/10000,/10000,/10000</t>
-        </is>
-      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
@@ -2073,7 +2041,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2084,12 +2052,12 @@
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站ID</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2101,15 +2069,11 @@
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>/10000</t>
-        </is>
-      </c>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2133,7 +2097,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2144,12 +2108,12 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站ID</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2161,15 +2125,11 @@
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>销售额(万元)</t>
+          <t>基站数</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>/10000</t>
-        </is>
-      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr">

--- a/cases/03_模板示例/项目配置.xlsx
+++ b/cases/03_模板示例/项目配置.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>#C8102E</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
@@ -768,7 +768,11 @@
           <t>月度PRB与速率趋势</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
     </row>
@@ -811,7 +815,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>#5B9BD5</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
@@ -866,7 +870,11 @@
           <t>地区基站数条形图</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
     </row>
